--- a/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_3b_dataset_comparison.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_3b_dataset_comparison.xlsx
@@ -568,23 +568,23 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_3b_dataset_comparison.xlsx
+++ b/experiments/03_dataset_comparison/report/dev_v1_original_vs_dev_v2_qwen_3b_dataset_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +52,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-        <bgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -173,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,20 +181,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1113,7 +1104,7 @@
       <c r="M9" s="5" t="n">
         <v>0.8845382532256466</v>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1124,7 +1115,7 @@
       <c r="P9" s="5" t="n">
         <v>0.7561739130434816</v>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1165,7 +1156,7 @@
       <c r="J10" s="5" t="n">
         <v>64.43614130434783</v>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1176,7 +1167,7 @@
       <c r="M10" s="5" t="n">
         <v>0.8453649683301563</v>
       </c>
-      <c r="N10" s="10" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1187,7 +1178,7 @@
       <c r="P10" s="5" t="n">
         <v>0.6737468139337289</v>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1228,7 +1219,7 @@
       <c r="J11" s="8" t="n">
         <v>84.23493044822257</v>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1239,7 +1230,7 @@
       <c r="M11" s="8" t="n">
         <v>0.8879255899755327</v>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
@@ -1250,7 +1241,7 @@
       <c r="P11" s="8" t="n">
         <v>0.7536886479975941</v>
       </c>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="Q11" s="9" t="inlineStr">
         <is>
           <t>dev_v1_original</t>
         </is>
